--- a/Upgrades.xlsx
+++ b/Upgrades.xlsx
@@ -4,19 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Consumables" sheetId="2" r:id="rId1"/>
     <sheet name="Shop" sheetId="1" r:id="rId2"/>
-    <sheet name="Лист3" sheetId="3" r:id="rId3"/>
+    <sheet name="Scars" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="84">
   <si>
     <t>Shopkeeper</t>
   </si>
@@ -60,52 +60,214 @@
     <t>Sacrifice</t>
   </si>
   <si>
-    <t>Select 1 unit to be destroyed and another unit to receive all of it's abilities</t>
-  </si>
-  <si>
-    <t>Remove 1 random ability</t>
-  </si>
-  <si>
     <t>Cleanse</t>
   </si>
   <si>
     <t>Up to 3 consumables can be stored. They can be applied to friendly units at any moment and their effects remain on the unit until the end of the game</t>
   </si>
   <si>
-    <t>Adds "Extra health(2)" to the unit</t>
+    <t>Adds "Safeguarded" to the unit</t>
+  </si>
+  <si>
+    <t>Attack mastery</t>
+  </si>
+  <si>
+    <t>Adds "Penetrating" to the unit</t>
+  </si>
+  <si>
+    <t>Movement mastery</t>
+  </si>
+  <si>
+    <t>Adds "Evading" to the unit</t>
+  </si>
+  <si>
+    <t>Destruction</t>
+  </si>
+  <si>
+    <t>Destroy the unit and remove it from your army</t>
+  </si>
+  <si>
+    <t>Copypaste</t>
+  </si>
+  <si>
+    <t>Receive the last upgrade used (Copypaste excluded)</t>
+  </si>
+  <si>
+    <t>Temporary vitality</t>
+  </si>
+  <si>
+    <t>Temporary protection</t>
+  </si>
+  <si>
+    <t>Select 1 unit to be sacrificed into an Ability token</t>
+  </si>
+  <si>
+    <t>Ability token</t>
+  </si>
+  <si>
+    <t>Select 1 unit to receive all abilities listed below                  (Ability1, Ability2…)</t>
+  </si>
+  <si>
+    <t>Remove 1 random ability                     (Prioritizes removing negative abilities)</t>
+  </si>
+  <si>
+    <t>Adds "Extra healthy(2)" to the unit</t>
+  </si>
+  <si>
+    <t>At the end of each battle, a "Scar assign" step is made. A d12 is rolled for each unit destroyed this turn. On a roll of a 1, this unit is "Scarred" and rolls one of the "Scars" from the table</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Blinded</t>
+  </si>
+  <si>
+    <t>Fatal wound</t>
+  </si>
+  <si>
+    <t>Captured</t>
+  </si>
+  <si>
+    <t>Wounded and weakened, the soldier is captured by the enemy. This unit is removed from your army, but will appear in the next shop and can be bought back</t>
+  </si>
+  <si>
+    <t>Broken</t>
+  </si>
+  <si>
+    <t>Amnesia</t>
+  </si>
+  <si>
+    <t>The injury leaves this soldier unable to recall or use most of their skills. This unit loses all Abilities gained from outside sources</t>
+  </si>
+  <si>
+    <t>Lasting wound</t>
+  </si>
+  <si>
+    <t>The wound is not fatal but cannot be fully healed either. This unit gains "Decaying"</t>
+  </si>
+  <si>
+    <t>Shell shock</t>
+  </si>
+  <si>
+    <t>Crippled</t>
+  </si>
+  <si>
+    <t>No vital organs were harmed, but the soldier is unable to move as swiftly as before. This unit gains "Slowed"</t>
+  </si>
+  <si>
+    <t>Discontent</t>
+  </si>
+  <si>
+    <t>Sickly</t>
+  </si>
+  <si>
+    <t>The wound is treated, but treated poorly. This unit gains "Vulnerable:Poison"</t>
+  </si>
+  <si>
+    <t>Insane</t>
+  </si>
+  <si>
+    <t>The wound is only second to the horrors this soldier experienced. This unit gains "Mad"</t>
+  </si>
+  <si>
+    <t>Limb trauma</t>
+  </si>
+  <si>
+    <t>Broken bones and pouring blood become addicting to the soldier. This unit gains "Bloodthirsty"</t>
+  </si>
+  <si>
+    <t>The wounds prove lethal and leave only a short while for the soldier to live. This unit is destroyed.</t>
+  </si>
+  <si>
+    <t>Small but precise wound leaves the soldier unable to focus on their targets. This unit gains "Blind"</t>
+  </si>
+  <si>
+    <t>The Thirst</t>
+  </si>
+  <si>
+    <t>Insomnia</t>
+  </si>
+  <si>
+    <t>The damage leaves this soldier permanently tired and unprepared. This unit gains "Delayed"</t>
+  </si>
+  <si>
+    <t>Minor wound</t>
+  </si>
+  <si>
+    <t>Recovering</t>
+  </si>
+  <si>
+    <t>Vulnerable</t>
+  </si>
+  <si>
+    <t>The new scars make for a poor defense. This unit's maximum health is decreased by 1 (To a minimum of 1)</t>
+  </si>
+  <si>
+    <t>Frail</t>
+  </si>
+  <si>
+    <t>Hasty recovery</t>
+  </si>
+  <si>
+    <t>No effect</t>
+  </si>
+  <si>
+    <t>Battle hardened</t>
+  </si>
+  <si>
+    <t>Costly treatment</t>
+  </si>
+  <si>
+    <t>Hysteria</t>
+  </si>
+  <si>
+    <t>The circumstances of the battle make this soldier terrified of being abandoned. This unit gains "Terrified"</t>
+  </si>
+  <si>
+    <t>The injury is not fatal but had severe psychological effects on the soldier. This unit cannot be deployed for the next 3 battles</t>
+  </si>
+  <si>
+    <t>The damage allows this soldier to overcome their weakness. This soldier loses one of their Negative abilities (If they have any)</t>
+  </si>
+  <si>
+    <t>The damage leaves the soldier broken and unable to follow orders. This unit gains "Unscoring"</t>
+  </si>
+  <si>
+    <t>The wound is permanent and requires an expensive treatment to ward off the simptoms. The unit gains "Costly"</t>
+  </si>
+  <si>
+    <t>The wound is treatable, but needs some time to heal. This unit cannot be deployed in the next battle</t>
+  </si>
+  <si>
+    <t>Tis' but a scratch. This unit starts the next battle with 1 less health (To a minimum of 1)</t>
   </si>
   <si>
     <t>Temporary might</t>
   </si>
   <si>
-    <t>Temporary shield</t>
-  </si>
-  <si>
-    <t>Adds "Safeguarded" to the unit</t>
-  </si>
-  <si>
-    <t>Attack mastery</t>
-  </si>
-  <si>
-    <t>Adds "Penetrating" to the unit</t>
-  </si>
-  <si>
-    <t>Movement mastery</t>
-  </si>
-  <si>
-    <t>Adds "Evading" to the unit</t>
-  </si>
-  <si>
-    <t>Destruction</t>
-  </si>
-  <si>
-    <t>Destroy the unit and remove it from your army</t>
-  </si>
-  <si>
-    <t>Copypaste</t>
-  </si>
-  <si>
-    <t>Receive the last upgrade used (Copypaste excluded)</t>
+    <t>Adds "Strengthened" to the unit</t>
+  </si>
+  <si>
+    <t>Flashbacks</t>
+  </si>
+  <si>
+    <t>The new scars weigh down all the limbs. This unit's attack damage is decreased by 1 (To a minimum of 0)</t>
+  </si>
+  <si>
+    <t>The soldier makes full recovery, but the sircumstances of the injury break their spirit. This unit gains "Paranoid"</t>
+  </si>
+  <si>
+    <t>Even after recovery, the soldier is still shaken. This unit gains "Weak"</t>
+  </si>
+  <si>
+    <t>Panic now plagues the soldier's mind. This unit gains "Cowardly"</t>
   </si>
 </sst>
 </file>
@@ -481,7 +643,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="2" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
@@ -498,6 +660,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -559,18 +748,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -878,107 +1055,125 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:J9"/>
+  <dimension ref="B1:L12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="35"/>
-    <col min="2" max="2" width="40.88671875" style="35" customWidth="1"/>
-    <col min="3" max="3" width="3.88671875" style="35" customWidth="1"/>
-    <col min="4" max="4" width="21.109375" style="35" customWidth="1"/>
-    <col min="5" max="5" width="4" style="35" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" style="35" customWidth="1"/>
-    <col min="7" max="7" width="3.6640625" style="35" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" style="35" customWidth="1"/>
-    <col min="9" max="9" width="3.109375" style="35" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="35" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="35"/>
+    <col min="1" max="1" width="8.88671875" style="14"/>
+    <col min="2" max="2" width="40.88671875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="3.88671875" style="14" customWidth="1"/>
+    <col min="4" max="4" width="21.109375" style="14" customWidth="1"/>
+    <col min="5" max="5" width="4" style="14" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" style="14" customWidth="1"/>
+    <col min="7" max="7" width="3.6640625" style="14" customWidth="1"/>
+    <col min="8" max="8" width="18.5546875" style="14" customWidth="1"/>
+    <col min="9" max="9" width="3.109375" style="14" customWidth="1"/>
+    <col min="10" max="10" width="15.6640625" style="14" customWidth="1"/>
+    <col min="11" max="11" width="8.88671875" style="14"/>
+    <col min="12" max="12" width="24.5546875" style="14" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:10" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:10" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+    <row r="1" spans="2:12" ht="9.6" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D8" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D9" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="D11" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" s="36" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="36" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="36" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="36" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" s="36" t="s">
-        <v>26</v>
-      </c>
-      <c r="J5" s="36" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="D6" s="36" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="36" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="D8" s="36" t="s">
+      <c r="F11" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="36" t="s">
+    </row>
+    <row r="12" spans="2:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="D12" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>20</v>
-      </c>
-      <c r="H8" s="36" t="s">
-        <v>22</v>
-      </c>
-      <c r="J8" s="36" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="D9" s="36" t="s">
-        <v>18</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="36" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="36" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1006,29 +1201,29 @@
   <sheetData>
     <row r="1" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="22"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="31"/>
     </row>
     <row r="3" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C3" s="5"/>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
-      <c r="F3" s="14" t="s">
+      <c r="F3" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="16"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="25"/>
       <c r="J3" s="6"/>
       <c r="K3" s="7"/>
       <c r="L3" s="8"/>
@@ -1037,10 +1232,10 @@
       <c r="C4" s="1"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="19"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="27"/>
+      <c r="I4" s="28"/>
       <c r="J4" s="2"/>
       <c r="K4" s="4"/>
       <c r="L4" s="3"/>
@@ -1077,20 +1272,20 @@
     </row>
     <row r="7" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C7" s="1"/>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="33"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="38" t="s">
         <v>2</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="38" t="s">
         <v>3</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="41" t="s">
         <v>4</v>
       </c>
       <c r="L7" s="3"/>
@@ -1099,62 +1294,62 @@
     </row>
     <row r="8" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C8" s="1"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="26"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="35"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="30"/>
+      <c r="G8" s="39"/>
       <c r="H8" s="2"/>
-      <c r="I8" s="30"/>
+      <c r="I8" s="39"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="33"/>
+      <c r="K8" s="42"/>
       <c r="L8" s="3"/>
     </row>
     <row r="9" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C9" s="1"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="26"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="35"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="30"/>
+      <c r="G9" s="39"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="30"/>
+      <c r="I9" s="39"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="33"/>
+      <c r="K9" s="42"/>
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C10" s="1"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="26"/>
+      <c r="D10" s="34"/>
+      <c r="E10" s="35"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="30"/>
+      <c r="G10" s="39"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="30"/>
+      <c r="I10" s="39"/>
       <c r="J10" s="2"/>
-      <c r="K10" s="33"/>
+      <c r="K10" s="42"/>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C11" s="1"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="26"/>
+      <c r="D11" s="34"/>
+      <c r="E11" s="35"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="30"/>
+      <c r="G11" s="39"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="30"/>
+      <c r="I11" s="39"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="33"/>
+      <c r="K11" s="42"/>
       <c r="L11" s="3"/>
     </row>
     <row r="12" spans="3:17" x14ac:dyDescent="0.3">
       <c r="C12" s="1"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="28"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="37"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="31"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="31"/>
+      <c r="I12" s="40"/>
       <c r="J12" s="2"/>
-      <c r="K12" s="34"/>
+      <c r="K12" s="43"/>
       <c r="L12" s="3"/>
     </row>
     <row r="13" spans="3:17" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1184,9 +1379,295 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="B1:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" style="18"/>
+    <col min="2" max="2" width="60.77734375" style="18" customWidth="1"/>
+    <col min="3" max="4" width="8.88671875" style="18"/>
+    <col min="5" max="5" width="20.6640625" style="18" customWidth="1"/>
+    <col min="6" max="6" width="106.109375" style="18" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:6" ht="57.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="22">
+        <v>1</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="B4" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="22">
+        <v>2</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="B5" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="22">
+        <v>3</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D6" s="22">
+        <v>4</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="22" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D7" s="22">
+        <v>5</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D8" s="22">
+        <v>6</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D9" s="22">
+        <v>7</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D10" s="22">
+        <v>8</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D11" s="22">
+        <v>9</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D12" s="22">
+        <v>10</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="22" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D13" s="22">
+        <v>11</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D14" s="22">
+        <v>12</v>
+      </c>
+      <c r="E14" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="22" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D15" s="22">
+        <v>13</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="D16" s="22">
+        <v>14</v>
+      </c>
+      <c r="E16" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D17" s="22">
+        <v>15</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D18" s="22">
+        <v>16</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D19" s="22">
+        <v>17</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D20" s="22">
+        <v>18</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D21" s="22">
+        <v>19</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D22" s="22">
+        <v>20</v>
+      </c>
+      <c r="E22" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D23" s="22">
+        <v>21</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D24" s="22">
+        <v>22</v>
+      </c>
+      <c r="E24" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="F24" s="22" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.3">
+      <c r="D25" s="22">
+        <v>23</v>
+      </c>
+      <c r="E25" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>